--- a/data/tra-nvs-quarterly-december-2024-2023.xlsx
+++ b/data/tra-nvs-quarterly-december-2024-2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\TRA\Surveys\NVS\NVS quarterly pubs\Website publication\Output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FIT3179-DV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA95FE44-8ABF-4A96-82DB-1A793B3C1308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16650" yWindow="255" windowWidth="20895" windowHeight="17400" tabRatio="827" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="827" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="2" r:id="rId1"/>
@@ -2837,17 +2837,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="11">
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="d/m/yy\ \ \ h:mm"/>
-    <numFmt numFmtId="165" formatCode="###\ ##0.0;\–###\ ##0"/>
-    <numFmt numFmtId="166" formatCode="#\ ##0"/>
-    <numFmt numFmtId="167" formatCode="###\ ##0;\–###\ ##0"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="0.0%"/>
-    <numFmt numFmtId="170" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="171" formatCode="[$-C09]d\ mmmm\ yyyy;@"/>
-    <numFmt numFmtId="172" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="d/m/yy\ \ \ h:mm"/>
+    <numFmt numFmtId="166" formatCode="###\ ##0.0;\–###\ ##0"/>
+    <numFmt numFmtId="167" formatCode="#\ ##0"/>
+    <numFmt numFmtId="168" formatCode="###\ ##0;\–###\ ##0"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.0%"/>
+    <numFmt numFmtId="171" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="172" formatCode="[$-C09]d\ mmmm\ yyyy;@"/>
+    <numFmt numFmtId="173" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="78">
     <font>
@@ -3717,7 +3717,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
@@ -3745,1151 +3745,1151 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="171" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="27" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="15" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="14" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="16" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="19" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="18" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="21" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="28" fillId="33" borderId="10"/>
-    <xf numFmtId="171" fontId="29" fillId="33" borderId="0"/>
-    <xf numFmtId="171" fontId="28" fillId="33" borderId="0"/>
+    <xf numFmtId="172" fontId="15" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="14" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="16" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="19" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="18" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="21" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="28" fillId="33" borderId="10"/>
+    <xf numFmtId="172" fontId="29" fillId="33" borderId="0"/>
+    <xf numFmtId="172" fontId="28" fillId="33" borderId="0"/>
     <xf numFmtId="49" fontId="30" fillId="0" borderId="0">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="31" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="32" fillId="0" borderId="0" applyNumberFormat="0">
+    <xf numFmtId="172" fontId="32" fillId="0" borderId="0" applyNumberFormat="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="33" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="34" fillId="0" borderId="11"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="27" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="34" fillId="0" borderId="11"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="27" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="28" fillId="33" borderId="0">
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="28" fillId="33" borderId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="28" fillId="33" borderId="10"/>
-    <xf numFmtId="171" fontId="29" fillId="33" borderId="0"/>
-    <xf numFmtId="171" fontId="28" fillId="33" borderId="0"/>
-    <xf numFmtId="170" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="28" fillId="33" borderId="10"/>
+    <xf numFmtId="172" fontId="29" fillId="33" borderId="0"/>
+    <xf numFmtId="172" fontId="28" fillId="33" borderId="0"/>
+    <xf numFmtId="171" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="173" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="35" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="32" fillId="0" borderId="0" applyNumberFormat="0">
+    <xf numFmtId="172" fontId="32" fillId="0" borderId="0" applyNumberFormat="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="33" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="34" fillId="0" borderId="11"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="33" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="34" fillId="0" borderId="11"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -4946,1111 +4946,1111 @@
     <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="171" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="15" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="14" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="16" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="19" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="18" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="21" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="15" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="14" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="16" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="19" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="11" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="18" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="21" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -6604,26 +6604,26 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
@@ -6636,10 +6636,10 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="69" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="69" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="61" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6655,7 +6655,7 @@
     <xf numFmtId="0" fontId="39" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="46" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="46" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="25" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -6671,7 +6671,7 @@
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="71" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="71" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6683,7 +6683,7 @@
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="61" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="61" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -6692,12 +6692,12 @@
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="25" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="46" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="46" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="64" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="61" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="42" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="64" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="61" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="42" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6718,13 +6718,13 @@
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="49" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="49" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="49" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="49" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="50" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="50" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6738,7 +6738,7 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="49" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="49" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="25" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -6761,19 +6761,19 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="50" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="50" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="60" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="60" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="46" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="46" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="46" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -6786,7 +6786,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="21" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="55" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="55" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6800,19 +6800,19 @@
     <xf numFmtId="1" fontId="46" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="46" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="46" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="42" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="42" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="61" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="61" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="50" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="50" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="50" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -6831,21 +6831,21 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="55" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="55" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="42" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="42" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="46" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="66" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="66" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="66" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="66" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -6897,7 +6897,7 @@
     </xf>
     <xf numFmtId="0" fontId="74" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="46" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -6918,13 +6918,13 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="49" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="49" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="55" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="55" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="50" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="50" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -10281,12 +10281,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F38"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="9" customWidth="1"/>
-    <col min="2" max="2" width="122.7109375" style="9" customWidth="1"/>
-    <col min="3" max="3" width="6.28515625" style="9" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="9"/>
+    <col min="1" max="1" width="10.6640625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="122.6640625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" style="9" customWidth="1"/>
+    <col min="4" max="16384" width="9.109375" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -10313,7 +10313,7 @@
       <c r="A6" s="32"/>
       <c r="B6" s="32"/>
     </row>
-    <row r="8" spans="1:6" ht="15">
+    <row r="8" spans="1:6" ht="16.2">
       <c r="A8" s="123" t="s">
         <v>355</v>
       </c>
@@ -10581,26 +10581,26 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L52"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="40.7109375" style="36" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" style="37" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" style="37" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" style="37" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="8.28515625" style="37" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.6640625" style="36" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" style="37" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" style="37" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" style="37" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.33203125" style="37" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="7" style="37" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" style="37" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.28515625" style="36"/>
+    <col min="10" max="10" width="9.5546875" style="37" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.33203125" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15">
+    <row r="1" spans="1:12" ht="14.4">
       <c r="A1" s="63"/>
       <c r="L1"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="63"/>
     </row>
-    <row r="3" spans="1:12" ht="25.15" customHeight="1">
+    <row r="3" spans="1:12" ht="25.2" customHeight="1">
       <c r="A3" s="99" t="s">
         <v>369</v>
       </c>
@@ -10615,7 +10615,7 @@
       <c r="J3" s="81"/>
       <c r="L3"/>
     </row>
-    <row r="4" spans="1:12" ht="14.25">
+    <row r="4" spans="1:12" ht="15">
       <c r="A4" s="95"/>
       <c r="B4" s="32" t="s">
         <v>0</v>
@@ -11025,7 +11025,7 @@
         <v>22810.242999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:10" s="24" customFormat="1" ht="14.25">
+    <row r="18" spans="1:10" s="24" customFormat="1" ht="13.8">
       <c r="A18" s="79" t="s">
         <v>236</v>
       </c>
@@ -11434,7 +11434,7 @@
         <v>24199.614000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="14.25">
+    <row r="32" spans="1:10" ht="13.8">
       <c r="A32" s="79" t="s">
         <v>236</v>
       </c>
@@ -11732,14 +11732,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J63"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" style="36" customWidth="1"/>
-    <col min="2" max="4" width="8.28515625" style="37" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" style="36" customWidth="1"/>
+    <col min="2" max="4" width="8.33203125" style="37" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" style="37" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.28515625" style="37" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.33203125" style="37" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="7" style="37" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.28515625" style="36"/>
+    <col min="10" max="16384" width="9.33203125" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -11788,7 +11788,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="14.25">
+    <row r="5" spans="1:9" ht="15">
       <c r="A5" s="95" t="s">
         <v>326</v>
       </c>
@@ -11914,7 +11914,7 @@
         <v>256.11</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="24" customFormat="1" ht="14.25">
+    <row r="11" spans="1:9" s="24" customFormat="1" ht="13.8">
       <c r="A11" s="67" t="s">
         <v>243</v>
       </c>
@@ -12054,7 +12054,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="24" customFormat="1" ht="14.25">
+    <row r="17" spans="1:9" s="24" customFormat="1" ht="13.8">
       <c r="A17" s="67" t="s">
         <v>243</v>
       </c>
@@ -12194,7 +12194,7 @@
         <v>256.11</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="24" customFormat="1" ht="14.25">
+    <row r="23" spans="1:9" s="24" customFormat="1" ht="13.8">
       <c r="A23" s="67" t="s">
         <v>243</v>
       </c>
@@ -12347,7 +12347,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="14.25">
+    <row r="30" spans="1:9" ht="13.8">
       <c r="A30" s="67" t="s">
         <v>243</v>
       </c>
@@ -12487,7 +12487,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="14.25">
+    <row r="36" spans="1:9" ht="13.8">
       <c r="A36" s="67" t="s">
         <v>243</v>
       </c>
@@ -12627,7 +12627,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="14.25">
+    <row r="42" spans="1:9" ht="13.8">
       <c r="A42" s="67" t="s">
         <v>243</v>
       </c>
@@ -12916,18 +12916,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J68"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="33.7109375" style="36" customWidth="1"/>
-    <col min="2" max="6" width="12.7109375" style="37" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="36" customWidth="1"/>
-    <col min="8" max="16384" width="9.28515625" style="36"/>
+    <col min="1" max="1" width="33.6640625" style="36" customWidth="1"/>
+    <col min="2" max="6" width="12.6640625" style="37" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" style="36" customWidth="1"/>
+    <col min="8" max="16384" width="9.33203125" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15">
+    <row r="1" spans="1:9" ht="14.4">
       <c r="I1"/>
     </row>
-    <row r="3" spans="1:9" ht="22.9" customHeight="1">
+    <row r="3" spans="1:9" ht="22.95" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>371</v>
       </c>
@@ -12957,7 +12957,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="16" customFormat="1" ht="15">
+    <row r="5" spans="1:9" s="16" customFormat="1" ht="14.4">
       <c r="A5" s="32" t="s">
         <v>275</v>
       </c>
@@ -12968,7 +12968,7 @@
       <c r="F5" s="20"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" ht="25.2">
       <c r="A6" s="32" t="s">
         <v>353</v>
       </c>
@@ -13407,7 +13407,7 @@
       <c r="F27" s="85"/>
       <c r="G27" s="4"/>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" ht="25.2">
       <c r="A28" s="32" t="s">
         <v>354</v>
       </c>
@@ -14015,15 +14015,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K73"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="36.5703125" style="36" customWidth="1"/>
-    <col min="2" max="6" width="12.7109375" style="37" customWidth="1"/>
-    <col min="7" max="7" width="6.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.28515625" style="36"/>
+    <col min="1" max="1" width="36.5546875" style="36" customWidth="1"/>
+    <col min="2" max="6" width="12.6640625" style="37" customWidth="1"/>
+    <col min="7" max="7" width="6.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.33203125" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8" ht="14.4">
       <c r="A1" s="63"/>
       <c r="G1"/>
     </row>
@@ -14031,7 +14031,7 @@
       <c r="A2" s="63"/>
       <c r="G2" s="36"/>
     </row>
-    <row r="3" spans="1:8" ht="28.15" customHeight="1">
+    <row r="3" spans="1:8" ht="28.2" customHeight="1">
       <c r="A3" s="99" t="s">
         <v>372</v>
       </c>
@@ -14042,7 +14042,7 @@
       <c r="F3" s="96"/>
       <c r="G3"/>
     </row>
-    <row r="4" spans="1:8" ht="38.25">
+    <row r="4" spans="1:8" ht="37.799999999999997">
       <c r="A4" s="20"/>
       <c r="B4" s="20" t="s">
         <v>17</v>
@@ -14061,7 +14061,7 @@
       </c>
       <c r="G4" s="17"/>
     </row>
-    <row r="5" spans="1:8" ht="15">
+    <row r="5" spans="1:8" ht="14.4">
       <c r="A5" s="15" t="s">
         <v>307</v>
       </c>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="G10" s="19"/>
     </row>
-    <row r="11" spans="1:8" s="24" customFormat="1" ht="14.25">
+    <row r="11" spans="1:8" s="24" customFormat="1" ht="13.8">
       <c r="A11" s="67" t="s">
         <v>248</v>
       </c>
@@ -14252,7 +14252,7 @@
       <c r="G15" s="40"/>
       <c r="H15" s="40"/>
     </row>
-    <row r="16" spans="1:8" s="24" customFormat="1" ht="14.25">
+    <row r="16" spans="1:8" s="24" customFormat="1" ht="13.8">
       <c r="A16" s="67" t="s">
         <v>248</v>
       </c>
@@ -14349,7 +14349,7 @@
       </c>
       <c r="G20" s="19"/>
     </row>
-    <row r="21" spans="1:11" s="24" customFormat="1" ht="14.25">
+    <row r="21" spans="1:11" s="24" customFormat="1" ht="13.8">
       <c r="A21" s="67" t="s">
         <v>248</v>
       </c>
@@ -14370,7 +14370,7 @@
       </c>
       <c r="G21" s="19"/>
     </row>
-    <row r="22" spans="1:11" ht="14.25">
+    <row r="22" spans="1:11" ht="13.8">
       <c r="A22" s="79" t="s">
         <v>249</v>
       </c>
@@ -14443,7 +14443,7 @@
       </c>
       <c r="G25" s="40"/>
     </row>
-    <row r="26" spans="1:11" s="24" customFormat="1" ht="14.25">
+    <row r="26" spans="1:11" s="24" customFormat="1" ht="13.8">
       <c r="A26" s="67" t="s">
         <v>248</v>
       </c>
@@ -14570,7 +14570,7 @@
       <c r="I32" s="84"/>
       <c r="J32" s="84"/>
     </row>
-    <row r="33" spans="1:7" ht="14.25">
+    <row r="33" spans="1:7" ht="13.8">
       <c r="A33" s="67" t="s">
         <v>248</v>
       </c>
@@ -14660,7 +14660,7 @@
         <v>598.03</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="14.25">
+    <row r="38" spans="1:7" ht="13.8">
       <c r="A38" s="67" t="s">
         <v>248</v>
       </c>
@@ -14750,7 +14750,7 @@
         <v>393.13</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="14.25">
+    <row r="43" spans="1:7" ht="13.8">
       <c r="A43" s="67" t="s">
         <v>248</v>
       </c>
@@ -14771,7 +14771,7 @@
       </c>
       <c r="G43" s="19"/>
     </row>
-    <row r="44" spans="1:7" ht="14.25">
+    <row r="44" spans="1:7" ht="13.8">
       <c r="A44" s="79" t="s">
         <v>249</v>
       </c>
@@ -14843,7 +14843,7 @@
         <v>6794.3469999999998</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="14.25">
+    <row r="48" spans="1:7" ht="13.8">
       <c r="A48" s="67" t="s">
         <v>248</v>
       </c>
@@ -15108,11 +15108,11 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:M61"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" style="36" customWidth="1"/>
-    <col min="2" max="7" width="18.7109375" style="37" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.28515625" style="36"/>
+    <col min="1" max="1" width="25.6640625" style="36" customWidth="1"/>
+    <col min="2" max="7" width="18.6640625" style="37" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.33203125" style="36"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:13">
@@ -15124,7 +15124,7 @@
       <c r="F2" s="87"/>
       <c r="G2" s="87"/>
     </row>
-    <row r="3" spans="1:13" ht="25.15" customHeight="1">
+    <row r="3" spans="1:13" ht="25.2" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>373</v>
       </c>
@@ -15141,7 +15141,7 @@
       <c r="L3" s="29"/>
       <c r="M3" s="29"/>
     </row>
-    <row r="4" spans="1:13" ht="38.25">
+    <row r="4" spans="1:13" ht="37.799999999999997">
       <c r="A4" s="12"/>
       <c r="B4" s="12" t="s">
         <v>329</v>
@@ -16097,15 +16097,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N69"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" style="36" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" style="36" customWidth="1"/>
-    <col min="3" max="14" width="19.5703125" style="112" customWidth="1"/>
-    <col min="15" max="16384" width="9.28515625" style="36"/>
+    <col min="1" max="1" width="7.6640625" style="36" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" style="36" customWidth="1"/>
+    <col min="3" max="14" width="19.5546875" style="112" customWidth="1"/>
+    <col min="15" max="16384" width="9.33203125" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15">
+    <row r="1" spans="1:14" ht="14.4">
       <c r="A1" s="63"/>
       <c r="B1" s="63"/>
       <c r="C1" s="111"/>
@@ -16120,7 +16120,7 @@
       <c r="B2" s="63"/>
       <c r="C2" s="111"/>
     </row>
-    <row r="3" spans="1:14" ht="18">
+    <row r="3" spans="1:14" ht="18.600000000000001">
       <c r="A3" s="102" t="s">
         <v>423</v>
       </c>
@@ -16135,7 +16135,7 @@
       <c r="M3" s="116"/>
       <c r="N3" s="116"/>
     </row>
-    <row r="4" spans="1:14" ht="15">
+    <row r="4" spans="1:14" ht="16.2">
       <c r="A4" s="102" t="s">
         <v>359</v>
       </c>
@@ -16150,7 +16150,7 @@
       <c r="M4" s="117"/>
       <c r="N4" s="116"/>
     </row>
-    <row r="5" spans="1:14" s="16" customFormat="1" ht="65.25">
+    <row r="5" spans="1:14" s="16" customFormat="1" ht="65.400000000000006">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
       <c r="C5" s="12" t="s">
@@ -18692,14 +18692,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J69"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" style="36" customWidth="1"/>
-    <col min="2" max="3" width="18.85546875" style="73" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" style="74" customWidth="1"/>
-    <col min="5" max="6" width="18.85546875" style="73" customWidth="1"/>
-    <col min="7" max="7" width="18.85546875" style="74" customWidth="1"/>
-    <col min="8" max="16384" width="9.28515625" style="36"/>
+    <col min="1" max="1" width="25.6640625" style="36" customWidth="1"/>
+    <col min="2" max="3" width="18.88671875" style="73" customWidth="1"/>
+    <col min="4" max="4" width="18.88671875" style="74" customWidth="1"/>
+    <col min="5" max="6" width="18.88671875" style="73" customWidth="1"/>
+    <col min="7" max="7" width="18.88671875" style="74" customWidth="1"/>
+    <col min="8" max="16384" width="9.33203125" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -18773,7 +18773,7 @@
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
     </row>
-    <row r="7" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="7" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A7" s="66" t="s">
         <v>17</v>
       </c>
@@ -18796,7 +18796,7 @@
         <v>7.1050000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="8" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A8" s="66" t="s">
         <v>18</v>
       </c>
@@ -18819,7 +18819,7 @@
         <v>-1.4410000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="9" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A9" s="66" t="s">
         <v>19</v>
       </c>
@@ -18842,7 +18842,7 @@
         <v>-34.883000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="10" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A10" s="66" t="s">
         <v>78</v>
       </c>
@@ -18865,7 +18865,7 @@
         <v>-9.4949999999999992</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="8" customFormat="1" ht="11.25">
+    <row r="11" spans="1:10" s="8" customFormat="1" ht="11.4">
       <c r="A11" s="67" t="s">
         <v>39</v>
       </c>
@@ -18899,7 +18899,7 @@
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
     </row>
-    <row r="13" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="13" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A13" s="66" t="s">
         <v>17</v>
       </c>
@@ -18922,7 +18922,7 @@
         <v>-2.5329999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="14" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A14" s="66" t="s">
         <v>18</v>
       </c>
@@ -18945,7 +18945,7 @@
         <v>-3.4769999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="15" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A15" s="66" t="s">
         <v>19</v>
       </c>
@@ -18968,7 +18968,7 @@
         <v>-37.951000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="16" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A16" s="66" t="s">
         <v>78</v>
       </c>
@@ -18991,7 +18991,7 @@
         <v>2.782</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="8" customFormat="1" ht="11.25">
+    <row r="17" spans="1:7" s="8" customFormat="1" ht="11.4">
       <c r="A17" s="67" t="s">
         <v>39</v>
       </c>
@@ -19025,7 +19025,7 @@
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
     </row>
-    <row r="19" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="19" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A19" s="66" t="s">
         <v>17</v>
       </c>
@@ -19048,7 +19048,7 @@
         <v>-7.0510000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="20" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A20" s="66" t="s">
         <v>18</v>
       </c>
@@ -19071,7 +19071,7 @@
         <v>3.2330000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="21" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A21" s="66" t="s">
         <v>19</v>
       </c>
@@ -19094,7 +19094,7 @@
         <v>-27.727</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="22" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A22" s="66" t="s">
         <v>78</v>
       </c>
@@ -19117,7 +19117,7 @@
         <v>-21.704000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="8" customFormat="1" ht="11.25">
+    <row r="23" spans="1:7" s="8" customFormat="1" ht="11.4">
       <c r="A23" s="67" t="s">
         <v>39</v>
       </c>
@@ -19151,7 +19151,7 @@
       <c r="F24" s="12"/>
       <c r="G24" s="12"/>
     </row>
-    <row r="25" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="25" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A25" s="66" t="s">
         <v>17</v>
       </c>
@@ -19174,7 +19174,7 @@
         <v>-27.384</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="26" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A26" s="66" t="s">
         <v>18</v>
       </c>
@@ -19197,7 +19197,7 @@
         <v>-8.1039999999999992</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="27" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A27" s="66" t="s">
         <v>19</v>
       </c>
@@ -19220,7 +19220,7 @@
         <v>-49.216000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="28" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A28" s="66" t="s">
         <v>78</v>
       </c>
@@ -19243,7 +19243,7 @@
         <v>27.513000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:7" s="8" customFormat="1" ht="11.25">
+    <row r="29" spans="1:7" s="8" customFormat="1" ht="11.4">
       <c r="A29" s="67" t="s">
         <v>39</v>
       </c>
@@ -19277,7 +19277,7 @@
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
     </row>
-    <row r="31" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="31" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A31" s="66" t="s">
         <v>17</v>
       </c>
@@ -19300,7 +19300,7 @@
         <v>-13.032999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="32" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A32" s="66" t="s">
         <v>18</v>
       </c>
@@ -19323,7 +19323,7 @@
         <v>-17.907</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="33" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A33" s="66" t="s">
         <v>19</v>
       </c>
@@ -19346,7 +19346,7 @@
         <v>21.263000000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="34" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A34" s="66" t="s">
         <v>78</v>
       </c>
@@ -19369,7 +19369,7 @@
         <v>17.323</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="8" customFormat="1" ht="11.25">
+    <row r="35" spans="1:7" s="8" customFormat="1" ht="11.4">
       <c r="A35" s="67" t="s">
         <v>39</v>
       </c>
@@ -19403,7 +19403,7 @@
       <c r="F36" s="12"/>
       <c r="G36" s="12"/>
     </row>
-    <row r="37" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="37" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A37" s="66" t="s">
         <v>17</v>
       </c>
@@ -19426,7 +19426,7 @@
         <v>7.9269999999999996</v>
       </c>
     </row>
-    <row r="38" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="38" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A38" s="66" t="s">
         <v>18</v>
       </c>
@@ -19449,7 +19449,7 @@
         <v>-17.36</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="39" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A39" s="66" t="s">
         <v>19</v>
       </c>
@@ -19472,7 +19472,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="40" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="40" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A40" s="66" t="s">
         <v>78</v>
       </c>
@@ -19495,7 +19495,7 @@
         <v>49.112000000000002</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="8" customFormat="1" ht="11.25">
+    <row r="41" spans="1:7" s="8" customFormat="1" ht="11.4">
       <c r="A41" s="67" t="s">
         <v>39</v>
       </c>
@@ -19529,7 +19529,7 @@
       <c r="F42" s="12"/>
       <c r="G42" s="12"/>
     </row>
-    <row r="43" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="43" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A43" s="66" t="s">
         <v>17</v>
       </c>
@@ -19552,7 +19552,7 @@
         <v>-3.4209999999999998</v>
       </c>
     </row>
-    <row r="44" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="44" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A44" s="66" t="s">
         <v>18</v>
       </c>
@@ -19575,7 +19575,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="45" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A45" s="66" t="s">
         <v>19</v>
       </c>
@@ -19598,7 +19598,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="46" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A46" s="66" t="s">
         <v>78</v>
       </c>
@@ -19621,7 +19621,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="8" customFormat="1" ht="11.25">
+    <row r="47" spans="1:7" s="8" customFormat="1" ht="11.4">
       <c r="A47" s="67" t="s">
         <v>39</v>
       </c>
@@ -19655,7 +19655,7 @@
       <c r="F48" s="12"/>
       <c r="G48" s="12"/>
     </row>
-    <row r="49" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="49" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A49" s="66" t="s">
         <v>17</v>
       </c>
@@ -19678,7 +19678,7 @@
         <v>-49.076999999999998</v>
       </c>
     </row>
-    <row r="50" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="50" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A50" s="66" t="s">
         <v>18</v>
       </c>
@@ -19701,7 +19701,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="51" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="51" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A51" s="66" t="s">
         <v>19</v>
       </c>
@@ -19724,7 +19724,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="52" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="52" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A52" s="66" t="s">
         <v>78</v>
       </c>
@@ -19747,7 +19747,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="53" spans="1:7" s="8" customFormat="1" ht="11.25">
+    <row r="53" spans="1:7" s="8" customFormat="1" ht="11.4">
       <c r="A53" s="67" t="s">
         <v>39</v>
       </c>
@@ -19781,7 +19781,7 @@
       <c r="F54" s="12"/>
       <c r="G54" s="12"/>
     </row>
-    <row r="55" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="55" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A55" s="66" t="s">
         <v>17</v>
       </c>
@@ -19804,7 +19804,7 @@
         <v>-4.4720000000000004</v>
       </c>
     </row>
-    <row r="56" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="56" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A56" s="66" t="s">
         <v>18</v>
       </c>
@@ -19827,7 +19827,7 @@
         <v>-3.859</v>
       </c>
     </row>
-    <row r="57" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="57" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A57" s="66" t="s">
         <v>19</v>
       </c>
@@ -19850,7 +19850,7 @@
         <v>-27.510999999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:7" s="34" customFormat="1" ht="11.25">
+    <row r="58" spans="1:7" s="34" customFormat="1" ht="11.4">
       <c r="A58" s="66" t="s">
         <v>78</v>
       </c>
@@ -19873,7 +19873,7 @@
         <v>-6.8140000000000001</v>
       </c>
     </row>
-    <row r="59" spans="1:7" s="8" customFormat="1" ht="11.25">
+    <row r="59" spans="1:7" s="8" customFormat="1" ht="11.4">
       <c r="A59" s="67" t="s">
         <v>39</v>
       </c>
@@ -20012,20 +20012,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J33"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="40.7109375" style="36" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" style="37" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" style="37" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="36" customWidth="1"/>
-    <col min="5" max="16384" width="9.28515625" style="36"/>
+    <col min="1" max="1" width="40.6640625" style="36" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" style="37" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" style="37" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="36" customWidth="1"/>
+    <col min="5" max="16384" width="9.33203125" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15">
+    <row r="1" spans="1:6" ht="14.4">
       <c r="A1" s="63"/>
       <c r="F1"/>
     </row>
-    <row r="2" spans="1:6" ht="15">
+    <row r="2" spans="1:6" ht="14.4">
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" ht="24.75" customHeight="1">
@@ -20038,7 +20038,7 @@
       <c r="E3" s="25"/>
       <c r="F3" s="54"/>
     </row>
-    <row r="4" spans="1:6" ht="25.5">
+    <row r="4" spans="1:6" ht="25.2">
       <c r="A4" s="32"/>
       <c r="B4" s="12" t="s">
         <v>357</v>
@@ -20054,7 +20054,7 @@
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
     </row>
-    <row r="6" spans="1:6" s="34" customFormat="1" ht="11.25">
+    <row r="6" spans="1:6" s="34" customFormat="1" ht="11.4">
       <c r="A6" s="39" t="s">
         <v>42</v>
       </c>
@@ -20066,7 +20066,7 @@
       </c>
       <c r="D6" s="31"/>
     </row>
-    <row r="7" spans="1:6" s="34" customFormat="1" ht="11.25">
+    <row r="7" spans="1:6" s="34" customFormat="1" ht="11.4">
       <c r="A7" s="39" t="s">
         <v>79</v>
       </c>
@@ -20078,7 +20078,7 @@
       </c>
       <c r="D7" s="31"/>
     </row>
-    <row r="8" spans="1:6" s="34" customFormat="1" ht="11.25">
+    <row r="8" spans="1:6" s="34" customFormat="1" ht="11.4">
       <c r="A8" s="39" t="s">
         <v>80</v>
       </c>
@@ -20090,7 +20090,7 @@
       </c>
       <c r="D8" s="31"/>
     </row>
-    <row r="9" spans="1:6" s="34" customFormat="1" ht="11.25">
+    <row r="9" spans="1:6" s="34" customFormat="1" ht="11.4">
       <c r="A9" s="39" t="s">
         <v>45</v>
       </c>
@@ -20102,7 +20102,7 @@
       </c>
       <c r="D9" s="31"/>
     </row>
-    <row r="10" spans="1:6" s="34" customFormat="1" ht="11.25">
+    <row r="10" spans="1:6" s="34" customFormat="1" ht="11.4">
       <c r="A10" s="39" t="s">
         <v>81</v>
       </c>
@@ -20114,7 +20114,7 @@
       </c>
       <c r="D10" s="31"/>
     </row>
-    <row r="11" spans="1:6" s="34" customFormat="1" ht="11.25">
+    <row r="11" spans="1:6" s="34" customFormat="1" ht="11.4">
       <c r="A11" s="39" t="s">
         <v>82</v>
       </c>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="D11" s="31"/>
     </row>
-    <row r="12" spans="1:6" s="34" customFormat="1" ht="11.25">
+    <row r="12" spans="1:6" s="34" customFormat="1" ht="11.4">
       <c r="A12" s="39" t="s">
         <v>83</v>
       </c>
@@ -20138,7 +20138,7 @@
       </c>
       <c r="D12" s="31"/>
     </row>
-    <row r="13" spans="1:6" s="34" customFormat="1" ht="11.25">
+    <row r="13" spans="1:6" s="34" customFormat="1" ht="11.4">
       <c r="A13" s="39" t="s">
         <v>49</v>
       </c>
@@ -20150,7 +20150,7 @@
       </c>
       <c r="D13" s="31"/>
     </row>
-    <row r="14" spans="1:6" s="34" customFormat="1" ht="11.25">
+    <row r="14" spans="1:6" s="34" customFormat="1" ht="11.4">
       <c r="A14" s="39" t="s">
         <v>50</v>
       </c>
@@ -20162,7 +20162,7 @@
       </c>
       <c r="D14" s="31"/>
     </row>
-    <row r="15" spans="1:6" s="34" customFormat="1" ht="11.25">
+    <row r="15" spans="1:6" s="34" customFormat="1" ht="11.4">
       <c r="A15" s="39" t="s">
         <v>84</v>
       </c>
@@ -20174,7 +20174,7 @@
       </c>
       <c r="D15" s="31"/>
     </row>
-    <row r="16" spans="1:6" s="34" customFormat="1" ht="11.25">
+    <row r="16" spans="1:6" s="34" customFormat="1" ht="11.4">
       <c r="A16" s="39" t="s">
         <v>53</v>
       </c>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="D16" s="31"/>
     </row>
-    <row r="17" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="17" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A17" s="39" t="s">
         <v>85</v>
       </c>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="D17" s="31"/>
     </row>
-    <row r="18" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="18" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A18" s="39" t="s">
         <v>86</v>
       </c>
@@ -20210,7 +20210,7 @@
       </c>
       <c r="D18" s="31"/>
     </row>
-    <row r="19" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="19" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A19" s="39" t="s">
         <v>56</v>
       </c>
@@ -20222,7 +20222,7 @@
       </c>
       <c r="D19" s="31"/>
     </row>
-    <row r="20" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="20" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A20" s="39" t="s">
         <v>57</v>
       </c>
@@ -20234,7 +20234,7 @@
       </c>
       <c r="D20" s="31"/>
     </row>
-    <row r="21" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="21" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A21" s="39" t="s">
         <v>58</v>
       </c>
@@ -20246,7 +20246,7 @@
       </c>
       <c r="D21" s="31"/>
     </row>
-    <row r="22" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="22" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A22" s="39" t="s">
         <v>87</v>
       </c>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="D22" s="31"/>
     </row>
-    <row r="23" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="23" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A23" s="39" t="s">
         <v>88</v>
       </c>
@@ -20270,7 +20270,7 @@
       </c>
       <c r="D23" s="31"/>
     </row>
-    <row r="24" spans="1:10" s="8" customFormat="1" ht="11.25">
+    <row r="24" spans="1:10" s="8" customFormat="1" ht="11.4">
       <c r="A24" s="79" t="s">
         <v>39</v>
       </c>
@@ -20354,18 +20354,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J46"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" style="36" customWidth="1"/>
-    <col min="2" max="5" width="20.7109375" style="37" customWidth="1"/>
-    <col min="6" max="16384" width="9.28515625" style="36"/>
+    <col min="1" max="1" width="25.6640625" style="36" customWidth="1"/>
+    <col min="2" max="5" width="20.6640625" style="37" customWidth="1"/>
+    <col min="6" max="16384" width="9.33203125" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15">
+    <row r="1" spans="1:10" ht="14.4">
       <c r="A1" s="63"/>
       <c r="F1"/>
     </row>
-    <row r="2" spans="1:10" ht="15">
+    <row r="2" spans="1:10" ht="14.4">
       <c r="A2" s="63"/>
       <c r="F2"/>
     </row>
@@ -20399,7 +20399,7 @@
       <c r="I4"/>
       <c r="J4"/>
     </row>
-    <row r="5" spans="1:10" s="34" customFormat="1" ht="25.5">
+    <row r="5" spans="1:10" s="34" customFormat="1" ht="25.2">
       <c r="A5" s="12"/>
       <c r="B5" s="12" t="s">
         <v>357</v>
@@ -20424,7 +20424,7 @@
       <c r="D6" s="32"/>
       <c r="E6" s="12"/>
     </row>
-    <row r="7" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="7" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A7" s="66" t="s">
         <v>76</v>
       </c>
@@ -20441,7 +20441,7 @@
         <v>3699.8989999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="8" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A8" s="66" t="s">
         <v>75</v>
       </c>
@@ -20458,7 +20458,7 @@
         <v>5956.9</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="9" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A9" s="67" t="s">
         <v>39</v>
       </c>
@@ -20484,7 +20484,7 @@
       <c r="D10" s="32"/>
       <c r="E10" s="12"/>
     </row>
-    <row r="11" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="11" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A11" s="66" t="s">
         <v>74</v>
       </c>
@@ -20501,7 +20501,7 @@
         <v>3153.0619999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="12" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A12" s="66" t="s">
         <v>73</v>
       </c>
@@ -20518,7 +20518,7 @@
         <v>4960.9409999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="13" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A13" s="67" t="s">
         <v>39</v>
       </c>
@@ -20544,7 +20544,7 @@
       <c r="D14" s="32"/>
       <c r="E14" s="12"/>
     </row>
-    <row r="15" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="15" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A15" s="66" t="s">
         <v>72</v>
       </c>
@@ -20561,7 +20561,7 @@
         <v>1152.6600000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="16" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A16" s="66" t="s">
         <v>71</v>
       </c>
@@ -20578,7 +20578,7 @@
         <v>2324.424</v>
       </c>
     </row>
-    <row r="17" spans="1:5" s="34" customFormat="1" ht="11.25">
+    <row r="17" spans="1:5" s="34" customFormat="1" ht="11.4">
       <c r="A17" s="66" t="s">
         <v>70</v>
       </c>
@@ -20595,7 +20595,7 @@
         <v>3055.8580000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:5" s="34" customFormat="1" ht="11.25">
+    <row r="18" spans="1:5" s="34" customFormat="1" ht="11.4">
       <c r="A18" s="67" t="s">
         <v>39</v>
       </c>
@@ -20621,7 +20621,7 @@
       <c r="D19" s="32"/>
       <c r="E19" s="12"/>
     </row>
-    <row r="20" spans="1:5" s="34" customFormat="1" ht="11.25">
+    <row r="20" spans="1:5" s="34" customFormat="1" ht="11.4">
       <c r="A20" s="66" t="s">
         <v>69</v>
       </c>
@@ -20638,7 +20638,7 @@
         <v>722.01400000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:5" s="34" customFormat="1" ht="11.25">
+    <row r="21" spans="1:5" s="34" customFormat="1" ht="11.4">
       <c r="A21" s="66" t="s">
         <v>68</v>
       </c>
@@ -20655,7 +20655,7 @@
         <v>1089.57</v>
       </c>
     </row>
-    <row r="22" spans="1:5" s="34" customFormat="1" ht="11.25">
+    <row r="22" spans="1:5" s="34" customFormat="1" ht="11.4">
       <c r="A22" s="67" t="s">
         <v>39</v>
       </c>
@@ -20681,7 +20681,7 @@
       <c r="D23" s="32"/>
       <c r="E23" s="12"/>
     </row>
-    <row r="24" spans="1:5" s="34" customFormat="1" ht="11.25">
+    <row r="24" spans="1:5" s="34" customFormat="1" ht="11.4">
       <c r="A24" s="66" t="s">
         <v>215</v>
       </c>
@@ -20698,7 +20698,7 @@
         <v>2033.27</v>
       </c>
     </row>
-    <row r="25" spans="1:5" s="34" customFormat="1" ht="11.25">
+    <row r="25" spans="1:5" s="34" customFormat="1" ht="11.4">
       <c r="A25" s="66" t="s">
         <v>67</v>
       </c>
@@ -20715,7 +20715,7 @@
         <v>1069.8240000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:5" s="34" customFormat="1" ht="11.25">
+    <row r="26" spans="1:5" s="34" customFormat="1" ht="11.4">
       <c r="A26" s="67" t="s">
         <v>39</v>
       </c>
@@ -20741,7 +20741,7 @@
       <c r="D27" s="32"/>
       <c r="E27" s="12"/>
     </row>
-    <row r="28" spans="1:5" s="34" customFormat="1" ht="11.25">
+    <row r="28" spans="1:5" s="34" customFormat="1" ht="11.4">
       <c r="A28" s="66" t="s">
         <v>216</v>
       </c>
@@ -20758,7 +20758,7 @@
         <v>360.47800000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:5" s="34" customFormat="1" ht="11.25">
+    <row r="29" spans="1:5" s="34" customFormat="1" ht="11.4">
       <c r="A29" s="66" t="s">
         <v>66</v>
       </c>
@@ -20775,7 +20775,7 @@
         <v>484.29199999999997</v>
       </c>
     </row>
-    <row r="30" spans="1:5" s="34" customFormat="1" ht="11.25">
+    <row r="30" spans="1:5" s="34" customFormat="1" ht="11.4">
       <c r="A30" s="67" t="s">
         <v>39</v>
       </c>
@@ -20801,7 +20801,7 @@
       <c r="D31" s="32"/>
       <c r="E31" s="12"/>
     </row>
-    <row r="32" spans="1:5" s="34" customFormat="1" ht="11.25">
+    <row r="32" spans="1:5" s="34" customFormat="1" ht="11.4">
       <c r="A32" s="66" t="s">
         <v>65</v>
       </c>
@@ -20818,7 +20818,7 @@
         <v>118.89400000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:8" s="34" customFormat="1" ht="11.25">
+    <row r="33" spans="1:8" s="34" customFormat="1" ht="11.4">
       <c r="A33" s="66" t="s">
         <v>64</v>
       </c>
@@ -20835,7 +20835,7 @@
         <v>84.602999999999994</v>
       </c>
     </row>
-    <row r="34" spans="1:8" s="34" customFormat="1" ht="11.25">
+    <row r="34" spans="1:8" s="34" customFormat="1" ht="11.4">
       <c r="A34" s="67" t="s">
         <v>39</v>
       </c>
@@ -20861,7 +20861,7 @@
       <c r="D35" s="32"/>
       <c r="E35" s="12"/>
     </row>
-    <row r="36" spans="1:8" s="34" customFormat="1" ht="11.25">
+    <row r="36" spans="1:8" s="34" customFormat="1" ht="11.4">
       <c r="A36" s="66" t="s">
         <v>5</v>
       </c>
@@ -20878,7 +20878,7 @@
         <v>406.83100000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:8" s="34" customFormat="1" ht="11.25">
+    <row r="37" spans="1:8" s="34" customFormat="1" ht="11.4">
       <c r="A37" s="67" t="s">
         <v>39</v>
       </c>
@@ -20904,7 +20904,7 @@
       <c r="D38" s="32"/>
       <c r="E38" s="12"/>
     </row>
-    <row r="39" spans="1:8" s="8" customFormat="1" ht="11.25">
+    <row r="39" spans="1:8" s="8" customFormat="1" ht="11.4">
       <c r="A39" s="67" t="s">
         <v>39</v>
       </c>
@@ -20990,15 +20990,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P67"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="36" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" style="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="20.85546875" style="37" customWidth="1"/>
-    <col min="9" max="16384" width="9.28515625" style="36"/>
+    <col min="1" max="1" width="5.6640625" style="36" customWidth="1"/>
+    <col min="2" max="2" width="34.6640625" style="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="20.88671875" style="37" customWidth="1"/>
+    <col min="9" max="16384" width="9.33203125" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15">
+    <row r="1" spans="1:16" ht="14.4">
       <c r="A1" s="63"/>
       <c r="B1" s="63"/>
       <c r="C1" s="87"/>
@@ -21011,7 +21011,7 @@
       <c r="O1"/>
       <c r="P1"/>
     </row>
-    <row r="2" spans="1:16" ht="15">
+    <row r="2" spans="1:16" ht="14.4">
       <c r="A2" s="63"/>
       <c r="B2" s="63"/>
       <c r="C2" s="87"/>
@@ -21024,7 +21024,7 @@
       <c r="O2"/>
       <c r="P2"/>
     </row>
-    <row r="3" spans="1:16" ht="18">
+    <row r="3" spans="1:16" ht="18.600000000000001">
       <c r="A3" s="26" t="s">
         <v>427</v>
       </c>
@@ -21044,7 +21044,7 @@
       <c r="O3"/>
       <c r="P3"/>
     </row>
-    <row r="4" spans="1:16" ht="15.75">
+    <row r="4" spans="1:16" ht="16.2">
       <c r="A4" s="26" t="s">
         <v>360</v>
       </c>
@@ -21117,7 +21117,7 @@
       </c>
       <c r="I6" s="101"/>
     </row>
-    <row r="7" spans="1:16" ht="15">
+    <row r="7" spans="1:16" ht="14.4">
       <c r="A7" s="104" t="s">
         <v>277</v>
       </c>
@@ -22568,17 +22568,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A3:K31"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="33.7109375" style="36" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="37" bestFit="1" customWidth="1"/>
-    <col min="3" max="9" width="7.7109375" style="37" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" style="37" customWidth="1"/>
-    <col min="11" max="11" width="8.7109375" style="36" customWidth="1"/>
-    <col min="12" max="16384" width="9.28515625" style="36"/>
+    <col min="1" max="1" width="33.6640625" style="36" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" style="37" bestFit="1" customWidth="1"/>
+    <col min="3" max="9" width="7.6640625" style="37" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="37" customWidth="1"/>
+    <col min="11" max="11" width="8.6640625" style="36" customWidth="1"/>
+    <col min="12" max="16384" width="9.33203125" style="36"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:11" ht="25.15" customHeight="1">
+    <row r="3" spans="1:11" ht="25.2" customHeight="1">
       <c r="A3" s="18" t="s">
         <v>361</v>
       </c>
@@ -22607,7 +22607,7 @@
       <c r="I4" s="97"/>
       <c r="J4" s="97"/>
     </row>
-    <row r="5" spans="1:11" ht="14.25">
+    <row r="5" spans="1:11" ht="15">
       <c r="A5" s="32"/>
       <c r="B5" s="12" t="s">
         <v>0</v>
@@ -22717,7 +22717,7 @@
       </c>
       <c r="K8" s="28"/>
     </row>
-    <row r="9" spans="1:11" ht="14.25">
+    <row r="9" spans="1:11" ht="13.8">
       <c r="A9" s="39" t="s">
         <v>316</v>
       </c>
@@ -22877,7 +22877,7 @@
       </c>
       <c r="K14" s="28"/>
     </row>
-    <row r="15" spans="1:11" ht="13.5">
+    <row r="15" spans="1:11" ht="15">
       <c r="A15" s="39" t="s">
         <v>340</v>
       </c>
@@ -23037,7 +23037,7 @@
       </c>
       <c r="K20" s="28"/>
     </row>
-    <row r="21" spans="1:11" ht="14.25">
+    <row r="21" spans="1:11" ht="13.8">
       <c r="A21" s="39" t="s">
         <v>317</v>
       </c>
@@ -23157,7 +23157,7 @@
       <c r="I26" s="46"/>
       <c r="J26" s="46"/>
     </row>
-    <row r="27" spans="1:11" s="43" customFormat="1" ht="11.25">
+    <row r="27" spans="1:11" s="43" customFormat="1" ht="11.4">
       <c r="A27" s="43" t="s">
         <v>430</v>
       </c>
@@ -23235,20 +23235,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J53"/>
-  <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="10.44140625" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" style="36" customWidth="1"/>
-    <col min="2" max="3" width="15.42578125" style="37" customWidth="1"/>
-    <col min="4" max="5" width="15.42578125" style="74" customWidth="1"/>
-    <col min="6" max="16384" width="10.42578125" style="36"/>
+    <col min="1" max="1" width="28.88671875" style="36" customWidth="1"/>
+    <col min="2" max="3" width="15.44140625" style="37" customWidth="1"/>
+    <col min="4" max="5" width="15.44140625" style="74" customWidth="1"/>
+    <col min="6" max="16384" width="10.44140625" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15">
+    <row r="1" spans="1:10" ht="14.4">
       <c r="A1" s="63"/>
       <c r="F1"/>
       <c r="G1"/>
     </row>
-    <row r="2" spans="1:10" ht="15">
+    <row r="2" spans="1:10" ht="14.4">
       <c r="A2" s="63"/>
       <c r="F2"/>
       <c r="G2"/>
@@ -23265,7 +23265,7 @@
       <c r="G3"/>
       <c r="J3" s="26"/>
     </row>
-    <row r="4" spans="1:10" ht="39.75">
+    <row r="4" spans="1:10" ht="40.200000000000003">
       <c r="A4" s="103"/>
       <c r="B4" s="12" t="s">
         <v>357</v>
@@ -23285,7 +23285,7 @@
       <c r="I4"/>
       <c r="J4"/>
     </row>
-    <row r="5" spans="1:10" ht="15">
+    <row r="5" spans="1:10" ht="14.4">
       <c r="A5" s="32" t="s">
         <v>307</v>
       </c>
@@ -23296,7 +23296,7 @@
       <c r="F5"/>
       <c r="G5"/>
     </row>
-    <row r="6" spans="1:10" ht="15">
+    <row r="6" spans="1:10" ht="14.4">
       <c r="A6" s="66" t="s">
         <v>17</v>
       </c>
@@ -23314,7 +23314,7 @@
       </c>
       <c r="G6"/>
     </row>
-    <row r="7" spans="1:10" ht="15">
+    <row r="7" spans="1:10" ht="14.4">
       <c r="A7" s="66" t="s">
         <v>18</v>
       </c>
@@ -23332,7 +23332,7 @@
       </c>
       <c r="G7"/>
     </row>
-    <row r="8" spans="1:10" ht="15">
+    <row r="8" spans="1:10" ht="14.4">
       <c r="A8" s="66" t="s">
         <v>19</v>
       </c>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="G8"/>
     </row>
-    <row r="9" spans="1:10" ht="15">
+    <row r="9" spans="1:10" ht="14.4">
       <c r="A9" s="66" t="s">
         <v>78</v>
       </c>
@@ -23368,7 +23368,7 @@
       </c>
       <c r="G9"/>
     </row>
-    <row r="10" spans="1:10" s="24" customFormat="1" ht="15">
+    <row r="10" spans="1:10" s="24" customFormat="1" ht="14.4">
       <c r="A10" s="67" t="s">
         <v>39</v>
       </c>
@@ -23386,7 +23386,7 @@
       </c>
       <c r="G10"/>
     </row>
-    <row r="11" spans="1:10" ht="15">
+    <row r="11" spans="1:10" ht="14.4">
       <c r="A11" s="66"/>
       <c r="B11" s="40"/>
       <c r="C11" s="40"/>
@@ -23394,7 +23394,7 @@
       <c r="E11" s="75"/>
       <c r="G11"/>
     </row>
-    <row r="12" spans="1:10" ht="15">
+    <row r="12" spans="1:10" ht="14.4">
       <c r="A12" s="32" t="s">
         <v>259</v>
       </c>
@@ -23404,7 +23404,7 @@
       <c r="E12" s="12"/>
       <c r="G12"/>
     </row>
-    <row r="13" spans="1:10" ht="15">
+    <row r="13" spans="1:10" ht="14.4">
       <c r="A13" s="66" t="s">
         <v>17</v>
       </c>
@@ -23422,7 +23422,7 @@
       </c>
       <c r="G13"/>
     </row>
-    <row r="14" spans="1:10" ht="15">
+    <row r="14" spans="1:10" ht="14.4">
       <c r="A14" s="66" t="s">
         <v>18</v>
       </c>
@@ -23440,7 +23440,7 @@
       </c>
       <c r="G14"/>
     </row>
-    <row r="15" spans="1:10" ht="15">
+    <row r="15" spans="1:10" ht="14.4">
       <c r="A15" s="66" t="s">
         <v>19</v>
       </c>
@@ -23458,7 +23458,7 @@
       </c>
       <c r="G15"/>
     </row>
-    <row r="16" spans="1:10" ht="15">
+    <row r="16" spans="1:10" ht="14.4">
       <c r="A16" s="66" t="s">
         <v>78</v>
       </c>
@@ -23478,7 +23478,7 @@
       <c r="H16" s="23"/>
       <c r="I16" s="23"/>
     </row>
-    <row r="17" spans="1:9" s="24" customFormat="1" ht="15">
+    <row r="17" spans="1:9" s="24" customFormat="1" ht="14.4">
       <c r="A17" s="67" t="s">
         <v>39</v>
       </c>
@@ -23498,7 +23498,7 @@
       <c r="H17" s="23"/>
       <c r="I17" s="23"/>
     </row>
-    <row r="18" spans="1:9" ht="15">
+    <row r="18" spans="1:9" ht="14.4">
       <c r="A18" s="66"/>
       <c r="B18" s="40"/>
       <c r="C18" s="40"/>
@@ -23506,7 +23506,7 @@
       <c r="E18" s="75"/>
       <c r="G18"/>
     </row>
-    <row r="19" spans="1:9" ht="15">
+    <row r="19" spans="1:9" ht="14.4">
       <c r="A19" s="32" t="s">
         <v>287</v>
       </c>
@@ -23516,7 +23516,7 @@
       <c r="E19" s="12"/>
       <c r="G19"/>
     </row>
-    <row r="20" spans="1:9" ht="15">
+    <row r="20" spans="1:9" ht="14.4">
       <c r="A20" s="66" t="s">
         <v>17</v>
       </c>
@@ -23534,7 +23534,7 @@
       </c>
       <c r="G20"/>
     </row>
-    <row r="21" spans="1:9" ht="15">
+    <row r="21" spans="1:9" ht="14.4">
       <c r="A21" s="66" t="s">
         <v>18</v>
       </c>
@@ -23552,7 +23552,7 @@
       </c>
       <c r="G21"/>
     </row>
-    <row r="22" spans="1:9" ht="15">
+    <row r="22" spans="1:9" ht="14.4">
       <c r="A22" s="66" t="s">
         <v>19</v>
       </c>
@@ -23570,7 +23570,7 @@
       </c>
       <c r="G22"/>
     </row>
-    <row r="23" spans="1:9" ht="15">
+    <row r="23" spans="1:9" ht="14.4">
       <c r="A23" s="66" t="s">
         <v>78</v>
       </c>
@@ -23588,7 +23588,7 @@
       </c>
       <c r="G23"/>
     </row>
-    <row r="24" spans="1:9" s="24" customFormat="1" ht="15">
+    <row r="24" spans="1:9" s="24" customFormat="1" ht="14.4">
       <c r="A24" s="67" t="s">
         <v>39</v>
       </c>
@@ -23606,7 +23606,7 @@
       </c>
       <c r="G24"/>
     </row>
-    <row r="25" spans="1:9" ht="15">
+    <row r="25" spans="1:9" ht="14.4">
       <c r="A25" s="34"/>
       <c r="B25" s="86"/>
       <c r="C25" s="86"/>
@@ -23614,7 +23614,7 @@
       <c r="E25" s="75"/>
       <c r="G25"/>
     </row>
-    <row r="26" spans="1:9" ht="15">
+    <row r="26" spans="1:9" ht="14.4">
       <c r="A26" s="95" t="s">
         <v>280</v>
       </c>
@@ -23624,7 +23624,7 @@
       <c r="E26" s="12"/>
       <c r="G26"/>
     </row>
-    <row r="27" spans="1:9" ht="15">
+    <row r="27" spans="1:9" ht="14.4">
       <c r="A27" s="66" t="s">
         <v>17</v>
       </c>
@@ -23638,7 +23638,7 @@
       <c r="E27" s="75"/>
       <c r="G27"/>
     </row>
-    <row r="28" spans="1:9" ht="15">
+    <row r="28" spans="1:9" ht="14.4">
       <c r="A28" s="66" t="s">
         <v>18</v>
       </c>
@@ -23652,7 +23652,7 @@
       <c r="E28" s="75"/>
       <c r="G28"/>
     </row>
-    <row r="29" spans="1:9" ht="15">
+    <row r="29" spans="1:9" ht="14.4">
       <c r="A29" s="66" t="s">
         <v>19</v>
       </c>
@@ -23666,7 +23666,7 @@
       <c r="E29" s="75"/>
       <c r="G29"/>
     </row>
-    <row r="30" spans="1:9" ht="15">
+    <row r="30" spans="1:9" ht="14.4">
       <c r="A30" s="66" t="s">
         <v>78</v>
       </c>
@@ -23680,7 +23680,7 @@
       <c r="E30" s="75"/>
       <c r="G30"/>
     </row>
-    <row r="31" spans="1:9" s="24" customFormat="1" ht="15">
+    <row r="31" spans="1:9" s="24" customFormat="1" ht="14.4">
       <c r="A31" s="67" t="s">
         <v>39</v>
       </c>
@@ -23694,7 +23694,7 @@
       <c r="E31" s="76"/>
       <c r="G31"/>
     </row>
-    <row r="32" spans="1:9" ht="15">
+    <row r="32" spans="1:9" ht="14.4">
       <c r="A32" s="66"/>
       <c r="B32" s="86"/>
       <c r="C32" s="93"/>
@@ -23702,7 +23702,7 @@
       <c r="E32" s="75"/>
       <c r="G32"/>
     </row>
-    <row r="33" spans="1:10" ht="15">
+    <row r="33" spans="1:10" ht="14.4">
       <c r="A33" s="95" t="s">
         <v>335</v>
       </c>
@@ -23712,7 +23712,7 @@
       <c r="E33" s="12"/>
       <c r="G33"/>
     </row>
-    <row r="34" spans="1:10" ht="15">
+    <row r="34" spans="1:10" ht="14.4">
       <c r="A34" s="66" t="s">
         <v>17</v>
       </c>
@@ -23726,7 +23726,7 @@
       <c r="E34" s="75"/>
       <c r="G34"/>
     </row>
-    <row r="35" spans="1:10" ht="15">
+    <row r="35" spans="1:10" ht="14.4">
       <c r="A35" s="66" t="s">
         <v>18</v>
       </c>
@@ -23740,7 +23740,7 @@
       <c r="E35" s="75"/>
       <c r="G35"/>
     </row>
-    <row r="36" spans="1:10" ht="15">
+    <row r="36" spans="1:10" ht="14.4">
       <c r="A36" s="66" t="s">
         <v>19</v>
       </c>
@@ -23754,7 +23754,7 @@
       <c r="E36" s="75"/>
       <c r="G36"/>
     </row>
-    <row r="37" spans="1:10" ht="15">
+    <row r="37" spans="1:10" ht="14.4">
       <c r="A37" s="66" t="s">
         <v>78</v>
       </c>
@@ -23768,7 +23768,7 @@
       <c r="E37" s="75"/>
       <c r="G37"/>
     </row>
-    <row r="38" spans="1:10" s="24" customFormat="1" ht="15">
+    <row r="38" spans="1:10" s="24" customFormat="1" ht="14.4">
       <c r="A38" s="67" t="s">
         <v>39</v>
       </c>
@@ -23782,7 +23782,7 @@
       <c r="E38" s="76"/>
       <c r="G38"/>
     </row>
-    <row r="39" spans="1:10" ht="15">
+    <row r="39" spans="1:10" ht="14.4">
       <c r="A39" s="66"/>
       <c r="B39" s="40"/>
       <c r="C39" s="40"/>
@@ -23790,7 +23790,7 @@
       <c r="E39" s="75"/>
       <c r="G39"/>
     </row>
-    <row r="40" spans="1:10" ht="15">
+    <row r="40" spans="1:10" ht="14.4">
       <c r="A40" s="95" t="s">
         <v>341</v>
       </c>
@@ -23941,19 +23941,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K102"/>
-  <sheetFormatPr defaultColWidth="10.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="10.44140625" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" style="36" customWidth="1"/>
-    <col min="2" max="3" width="15.42578125" style="37" customWidth="1"/>
-    <col min="4" max="5" width="15.42578125" style="74" customWidth="1"/>
-    <col min="6" max="16384" width="10.42578125" style="36"/>
+    <col min="1" max="1" width="28.88671875" style="36" customWidth="1"/>
+    <col min="2" max="3" width="15.44140625" style="37" customWidth="1"/>
+    <col min="4" max="5" width="15.44140625" style="74" customWidth="1"/>
+    <col min="6" max="16384" width="10.44140625" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15">
+    <row r="1" spans="1:11" ht="14.4">
       <c r="A1" s="63"/>
       <c r="F1"/>
     </row>
-    <row r="2" spans="1:11" ht="15">
+    <row r="2" spans="1:11" ht="14.4">
       <c r="A2" s="63"/>
       <c r="F2"/>
     </row>
@@ -23967,7 +23967,7 @@
       <c r="E3" s="96"/>
       <c r="F3"/>
     </row>
-    <row r="4" spans="1:11" ht="39.75">
+    <row r="4" spans="1:11" ht="40.200000000000003">
       <c r="A4" s="103"/>
       <c r="B4" s="12" t="s">
         <v>357</v>
@@ -23988,7 +23988,7 @@
       <c r="J4"/>
       <c r="K4"/>
     </row>
-    <row r="5" spans="1:11" ht="15">
+    <row r="5" spans="1:11" ht="14.4">
       <c r="A5" s="32" t="s">
         <v>307</v>
       </c>
@@ -24496,7 +24496,7 @@
       <c r="E34" s="75"/>
       <c r="G34" s="30"/>
     </row>
-    <row r="35" spans="1:7" ht="15">
+    <row r="35" spans="1:7" ht="14.4">
       <c r="A35" s="32" t="s">
         <v>259</v>
       </c>
@@ -24999,7 +24999,7 @@
       <c r="D64" s="75"/>
       <c r="E64" s="75"/>
     </row>
-    <row r="65" spans="1:6" ht="15">
+    <row r="65" spans="1:6" ht="14.4">
       <c r="A65" s="32" t="s">
         <v>287</v>
       </c>
@@ -25585,9 +25585,9 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C89"/>
-  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="2" width="68.140625" customWidth="1"/>
+    <col min="1" max="2" width="68.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -26170,16 +26170,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A3:K37"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="33.7109375" style="36" customWidth="1"/>
-    <col min="2" max="9" width="7.7109375" style="37" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" style="37" customWidth="1"/>
-    <col min="11" max="11" width="8.7109375" style="36" customWidth="1"/>
-    <col min="12" max="16384" width="9.28515625" style="36"/>
+    <col min="1" max="1" width="33.6640625" style="36" customWidth="1"/>
+    <col min="2" max="9" width="7.6640625" style="37" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="37" customWidth="1"/>
+    <col min="11" max="11" width="8.6640625" style="36" customWidth="1"/>
+    <col min="12" max="16384" width="9.33203125" style="36"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:11" ht="26.45" customHeight="1">
+    <row r="3" spans="1:11" ht="26.4" customHeight="1">
       <c r="A3" s="18" t="s">
         <v>362</v>
       </c>
@@ -26208,7 +26208,7 @@
       <c r="I4" s="97"/>
       <c r="J4" s="97"/>
     </row>
-    <row r="5" spans="1:11" ht="14.25">
+    <row r="5" spans="1:11" ht="15">
       <c r="A5" s="32"/>
       <c r="B5" s="12" t="s">
         <v>0</v>
@@ -26318,7 +26318,7 @@
       </c>
       <c r="K8" s="28"/>
     </row>
-    <row r="9" spans="1:11" ht="13.5">
+    <row r="9" spans="1:11" ht="15">
       <c r="A9" s="39" t="s">
         <v>318</v>
       </c>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="K14" s="28"/>
     </row>
-    <row r="15" spans="1:11" ht="13.5">
+    <row r="15" spans="1:11" ht="15">
       <c r="A15" s="39" t="s">
         <v>339</v>
       </c>
@@ -26638,7 +26638,7 @@
       </c>
       <c r="K20" s="28"/>
     </row>
-    <row r="21" spans="1:11" ht="13.5">
+    <row r="21" spans="1:11" ht="15">
       <c r="A21" s="39" t="s">
         <v>319</v>
       </c>
@@ -26773,7 +26773,7 @@
       <c r="I27" s="46"/>
       <c r="J27" s="46"/>
     </row>
-    <row r="28" spans="1:11" s="43" customFormat="1" ht="11.25">
+    <row r="28" spans="1:11" s="43" customFormat="1" ht="11.4">
       <c r="A28" s="43" t="s">
         <v>432</v>
       </c>
@@ -26790,7 +26790,7 @@
       <c r="I29" s="46"/>
       <c r="J29" s="46"/>
     </row>
-    <row r="30" spans="1:11" s="110" customFormat="1">
+    <row r="30" spans="1:11" s="110" customFormat="1" ht="13.8">
       <c r="A30" s="80" t="s">
         <v>313</v>
       </c>
@@ -26916,12 +26916,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A3:K46"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="33.7109375" style="36" customWidth="1"/>
-    <col min="2" max="6" width="12.7109375" style="37" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="36" customWidth="1"/>
-    <col min="8" max="16384" width="9.28515625" style="36"/>
+    <col min="1" max="1" width="33.6640625" style="36" customWidth="1"/>
+    <col min="2" max="6" width="12.6640625" style="37" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" style="36" customWidth="1"/>
+    <col min="8" max="16384" width="9.33203125" style="36"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:11" s="38" customFormat="1" ht="21.6" customHeight="1">
@@ -27020,7 +27020,7 @@
       </c>
       <c r="G8" s="28"/>
     </row>
-    <row r="9" spans="1:11" ht="13.5">
+    <row r="9" spans="1:11" ht="15">
       <c r="A9" s="39" t="s">
         <v>320</v>
       </c>
@@ -27124,7 +27124,7 @@
       </c>
       <c r="G14" s="28"/>
     </row>
-    <row r="15" spans="1:11" ht="13.5">
+    <row r="15" spans="1:11" ht="15">
       <c r="A15" s="39" t="s">
         <v>338</v>
       </c>
@@ -27175,7 +27175,7 @@
       <c r="F17" s="40"/>
       <c r="G17" s="28"/>
     </row>
-    <row r="18" spans="1:11" ht="14.25">
+    <row r="18" spans="1:11" ht="15">
       <c r="A18" s="32" t="s">
         <v>265</v>
       </c>
@@ -27228,7 +27228,7 @@
       </c>
       <c r="G20" s="28"/>
     </row>
-    <row r="21" spans="1:11" ht="13.5">
+    <row r="21" spans="1:11" ht="15">
       <c r="A21" s="39" t="s">
         <v>321</v>
       </c>
@@ -27368,7 +27368,7 @@
       <c r="H30" s="21"/>
       <c r="I30" s="21"/>
     </row>
-    <row r="31" spans="1:11" s="110" customFormat="1">
+    <row r="31" spans="1:11" s="110" customFormat="1" ht="13.8">
       <c r="A31" s="80" t="s">
         <v>313</v>
       </c>
@@ -27520,12 +27520,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J42"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="33.7109375" style="36" customWidth="1"/>
-    <col min="2" max="6" width="12.7109375" style="37" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="36" customWidth="1"/>
-    <col min="8" max="16384" width="9.28515625" style="36"/>
+    <col min="1" max="1" width="33.6640625" style="36" customWidth="1"/>
+    <col min="2" max="6" width="12.6640625" style="37" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" style="36" customWidth="1"/>
+    <col min="8" max="16384" width="9.33203125" style="36"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -27545,7 +27545,7 @@
       <c r="F3" s="64"/>
       <c r="G3" s="58"/>
     </row>
-    <row r="4" spans="1:7" ht="19.899999999999999" customHeight="1">
+    <row r="4" spans="1:7" ht="19.95" customHeight="1">
       <c r="A4" s="18" t="s">
         <v>267</v>
       </c>
@@ -27556,7 +27556,7 @@
       <c r="F4" s="56"/>
       <c r="G4" s="58"/>
     </row>
-    <row r="5" spans="1:7" ht="38.25">
+    <row r="5" spans="1:7" ht="37.799999999999997">
       <c r="A5" s="32"/>
       <c r="B5" s="20" t="s">
         <v>17</v>
@@ -27626,7 +27626,7 @@
       </c>
       <c r="G8" s="28"/>
     </row>
-    <row r="9" spans="1:7" ht="13.5">
+    <row r="9" spans="1:7" ht="15">
       <c r="A9" s="39" t="s">
         <v>321</v>
       </c>
@@ -27729,7 +27729,7 @@
       </c>
       <c r="G14" s="28"/>
     </row>
-    <row r="15" spans="1:7" ht="13.5">
+    <row r="15" spans="1:7" ht="15">
       <c r="A15" s="39" t="s">
         <v>337</v>
       </c>
@@ -27780,7 +27780,7 @@
       <c r="F17" s="40"/>
       <c r="G17" s="28"/>
     </row>
-    <row r="18" spans="1:10" ht="14.25">
+    <row r="18" spans="1:10" ht="15">
       <c r="A18" s="32" t="s">
         <v>266</v>
       </c>
@@ -27832,7 +27832,7 @@
       </c>
       <c r="G20" s="28"/>
     </row>
-    <row r="21" spans="1:10" ht="13.5">
+    <row r="21" spans="1:10" ht="15">
       <c r="A21" s="39" t="s">
         <v>323</v>
       </c>
@@ -28046,21 +28046,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A3:J72"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="35.42578125" style="36" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="35.44140625" style="36" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" style="37" customWidth="1"/>
     <col min="3" max="3" width="11" style="37" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" style="37" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" style="37" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" style="37" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" style="37" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" style="37" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" style="37" customWidth="1"/>
     <col min="7" max="7" width="9" style="37" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" style="37" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" style="37" customWidth="1"/>
-    <col min="10" max="16384" width="9.28515625" style="36"/>
+    <col min="8" max="8" width="9.44140625" style="37" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" style="37" customWidth="1"/>
+    <col min="10" max="16384" width="9.33203125" style="36"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:9" ht="23.45" customHeight="1">
+    <row r="3" spans="1:9" ht="23.4" customHeight="1">
       <c r="A3" s="18" t="s">
         <v>365</v>
       </c>
@@ -28255,7 +28255,7 @@
         <v>325.08800000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="14.25">
+    <row r="12" spans="1:9" ht="13.8">
       <c r="A12" s="67" t="s">
         <v>236</v>
       </c>
@@ -28424,7 +28424,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="14.25">
+    <row r="19" spans="1:9" ht="13.8">
       <c r="A19" s="67" t="s">
         <v>236</v>
       </c>
@@ -28593,7 +28593,7 @@
         <v>325.08800000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="14.25">
+    <row r="26" spans="1:9" ht="13.8">
       <c r="A26" s="67" t="s">
         <v>236</v>
       </c>
@@ -28622,7 +28622,7 @@
         <v>3298.1129999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15">
+    <row r="27" spans="1:9" ht="16.2">
       <c r="A27" s="69"/>
       <c r="B27" s="70"/>
       <c r="C27" s="70"/>
@@ -28775,7 +28775,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="14.25">
+    <row r="34" spans="1:9" ht="13.8">
       <c r="A34" s="67" t="s">
         <v>236</v>
       </c>
@@ -28944,7 +28944,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="14.25">
+    <row r="41" spans="1:9" ht="13.8">
       <c r="A41" s="67" t="s">
         <v>236</v>
       </c>
@@ -29113,7 +29113,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="14.25">
+    <row r="48" spans="1:9" ht="13.8">
       <c r="A48" s="67" t="s">
         <v>236</v>
       </c>
@@ -29434,22 +29434,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A3:K71"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" style="36" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" style="37" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" style="37" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" style="37" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" style="37" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" style="36" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" style="37" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="37" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" style="37" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="37" customWidth="1"/>
     <col min="6" max="6" width="9" style="37" customWidth="1"/>
-    <col min="7" max="7" width="8.42578125" style="37" customWidth="1"/>
+    <col min="7" max="7" width="8.44140625" style="37" customWidth="1"/>
     <col min="8" max="8" width="9" style="37" customWidth="1"/>
-    <col min="9" max="9" width="8.85546875" style="37" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="37" customWidth="1"/>
     <col min="10" max="10" width="10" style="37" customWidth="1"/>
-    <col min="11" max="16384" width="9.28515625" style="36"/>
+    <col min="11" max="16384" width="9.33203125" style="36"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:10" ht="25.9" customHeight="1">
+    <row r="3" spans="1:10" ht="25.95" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>366</v>
       </c>
@@ -29507,7 +29507,7 @@
       <c r="I5" s="32"/>
       <c r="J5" s="32"/>
     </row>
-    <row r="6" spans="1:10" s="34" customFormat="1" ht="25.5">
+    <row r="6" spans="1:10" s="34" customFormat="1" ht="25.2">
       <c r="A6" s="32" t="s">
         <v>353</v>
       </c>
@@ -29535,7 +29535,7 @@
       <c r="I7" s="32"/>
       <c r="J7" s="32"/>
     </row>
-    <row r="8" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="8" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A8" s="66" t="s">
         <v>17</v>
       </c>
@@ -29567,7 +29567,7 @@
         <v>70793.66</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="9" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A9" s="66" t="s">
         <v>18</v>
       </c>
@@ -29599,7 +29599,7 @@
         <v>55763.536999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="10" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A10" s="66" t="s">
         <v>19</v>
       </c>
@@ -29631,7 +29631,7 @@
         <v>35011.171000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="11" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A11" s="66" t="s">
         <v>20</v>
       </c>
@@ -29663,7 +29663,7 @@
         <v>6305.0649999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="34" customFormat="1" ht="14.25">
+    <row r="12" spans="1:10" s="34" customFormat="1" ht="13.8">
       <c r="A12" s="67" t="s">
         <v>236</v>
       </c>
@@ -29695,7 +29695,7 @@
         <v>168150.228</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="13" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A13" s="66"/>
       <c r="B13" s="41"/>
       <c r="C13" s="41"/>
@@ -29721,7 +29721,7 @@
       <c r="I14" s="32"/>
       <c r="J14" s="32"/>
     </row>
-    <row r="15" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="15" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A15" s="66" t="s">
         <v>17</v>
       </c>
@@ -29753,7 +29753,7 @@
         <v>105793.58199999999</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="16" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A16" s="66" t="s">
         <v>18</v>
       </c>
@@ -29785,7 +29785,7 @@
         <v>64276.207999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:11" s="34" customFormat="1" ht="11.25">
+    <row r="17" spans="1:11" s="34" customFormat="1" ht="11.4">
       <c r="A17" s="66" t="s">
         <v>19</v>
       </c>
@@ -29817,7 +29817,7 @@
         <v>49307.794999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:11" s="34" customFormat="1" ht="11.25">
+    <row r="18" spans="1:11" s="34" customFormat="1" ht="11.4">
       <c r="A18" s="66" t="s">
         <v>20</v>
       </c>
@@ -29849,7 +29849,7 @@
         <v>14881.186</v>
       </c>
     </row>
-    <row r="19" spans="1:11" s="34" customFormat="1" ht="14.25">
+    <row r="19" spans="1:11" s="34" customFormat="1" ht="13.8">
       <c r="A19" s="67" t="s">
         <v>236</v>
       </c>
@@ -29881,7 +29881,7 @@
         <v>234296.94200000001</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="34" customFormat="1" ht="11.25">
+    <row r="20" spans="1:11" s="34" customFormat="1" ht="11.4">
       <c r="A20" s="66"/>
       <c r="B20" s="41"/>
       <c r="C20" s="41"/>
@@ -29907,7 +29907,7 @@
       <c r="I21" s="32"/>
       <c r="J21" s="32"/>
     </row>
-    <row r="22" spans="1:11" s="34" customFormat="1" ht="11.25">
+    <row r="22" spans="1:11" s="34" customFormat="1" ht="11.4">
       <c r="A22" s="66" t="s">
         <v>17</v>
       </c>
@@ -29939,7 +29939,7 @@
         <v>176587.24299999999</v>
       </c>
     </row>
-    <row r="23" spans="1:11" s="34" customFormat="1" ht="11.25">
+    <row r="23" spans="1:11" s="34" customFormat="1" ht="11.4">
       <c r="A23" s="66" t="s">
         <v>18</v>
       </c>
@@ -29971,7 +29971,7 @@
         <v>120039.74400000001</v>
       </c>
     </row>
-    <row r="24" spans="1:11" s="34" customFormat="1" ht="11.25">
+    <row r="24" spans="1:11" s="34" customFormat="1" ht="11.4">
       <c r="A24" s="66" t="s">
         <v>19</v>
       </c>
@@ -30003,7 +30003,7 @@
         <v>84318.966</v>
       </c>
     </row>
-    <row r="25" spans="1:11" s="34" customFormat="1" ht="11.25">
+    <row r="25" spans="1:11" s="34" customFormat="1" ht="11.4">
       <c r="A25" s="66" t="s">
         <v>20</v>
       </c>
@@ -30035,7 +30035,7 @@
         <v>21186.251</v>
       </c>
     </row>
-    <row r="26" spans="1:11" s="34" customFormat="1" ht="14.25">
+    <row r="26" spans="1:11" s="34" customFormat="1" ht="13.8">
       <c r="A26" s="67" t="s">
         <v>236</v>
       </c>
@@ -30068,7 +30068,7 @@
       </c>
       <c r="K26" s="8"/>
     </row>
-    <row r="27" spans="1:11" s="34" customFormat="1" ht="11.25">
+    <row r="27" spans="1:11" s="34" customFormat="1" ht="11.4">
       <c r="A27" s="66"/>
       <c r="B27" s="41"/>
       <c r="C27" s="41"/>
@@ -30080,7 +30080,7 @@
       <c r="I27" s="41"/>
       <c r="J27" s="41"/>
     </row>
-    <row r="28" spans="1:11" ht="25.5">
+    <row r="28" spans="1:11" ht="25.2">
       <c r="A28" s="32" t="s">
         <v>354</v>
       </c>
@@ -30236,7 +30236,7 @@
         <v>6471.93</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="14.25">
+    <row r="34" spans="1:10" ht="13.8">
       <c r="A34" s="67" t="s">
         <v>236</v>
       </c>
@@ -30422,7 +30422,7 @@
         <v>13094.22</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="14.25">
+    <row r="41" spans="1:10" ht="13.8">
       <c r="A41" s="67" t="s">
         <v>236</v>
       </c>
@@ -30608,7 +30608,7 @@
         <v>19566.150000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="14.25">
+    <row r="48" spans="1:10" ht="13.8">
       <c r="A48" s="67" t="s">
         <v>236</v>
       </c>
@@ -30938,20 +30938,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M69"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" style="36" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" style="36" customWidth="1"/>
     <col min="2" max="2" width="20" style="73" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" style="73" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="74" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" style="73" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" style="74" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="19" style="74" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="74" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" style="74" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="19" style="73" customWidth="1"/>
-    <col min="10" max="10" width="19.7109375" style="74" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.28515625" style="36"/>
+    <col min="10" max="10" width="19.6640625" style="74" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.33203125" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15">
+    <row r="1" spans="1:10" ht="14.4">
       <c r="A1" s="63"/>
       <c r="E1"/>
       <c r="H1"/>
@@ -30959,7 +30959,7 @@
     <row r="2" spans="1:10">
       <c r="A2" s="63"/>
     </row>
-    <row r="3" spans="1:10" ht="26.45" customHeight="1">
+    <row r="3" spans="1:10" ht="26.4" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>367</v>
       </c>
@@ -30973,7 +30973,7 @@
       <c r="I3" s="55"/>
       <c r="J3" s="55"/>
     </row>
-    <row r="4" spans="1:10" ht="44.45" customHeight="1">
+    <row r="4" spans="1:10" ht="44.4" customHeight="1">
       <c r="A4" s="32"/>
       <c r="B4" s="12" t="s">
         <v>307</v>
@@ -31047,7 +31047,7 @@
       <c r="I6" s="32"/>
       <c r="J6" s="32"/>
     </row>
-    <row r="7" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="7" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A7" s="66" t="s">
         <v>17</v>
       </c>
@@ -31079,7 +31079,7 @@
         <v>1.99</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="8" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A8" s="66" t="s">
         <v>18</v>
       </c>
@@ -31111,7 +31111,7 @@
         <v>-1.7210000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="9" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A9" s="66" t="s">
         <v>19</v>
       </c>
@@ -31143,7 +31143,7 @@
         <v>-0.90700000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="10" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A10" s="66" t="s">
         <v>78</v>
       </c>
@@ -31175,7 +31175,7 @@
         <v>12.587</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="8" customFormat="1" ht="11.25">
+    <row r="11" spans="1:10" s="8" customFormat="1" ht="11.4">
       <c r="A11" s="67" t="s">
         <v>39</v>
       </c>
@@ -31221,7 +31221,7 @@
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
     </row>
-    <row r="13" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="13" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A13" s="66" t="s">
         <v>17</v>
       </c>
@@ -31253,7 +31253,7 @@
         <v>4.7270000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="14" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A14" s="66" t="s">
         <v>18</v>
       </c>
@@ -31285,7 +31285,7 @@
         <v>-11.351000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="15" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A15" s="66" t="s">
         <v>19</v>
       </c>
@@ -31317,7 +31317,7 @@
         <v>-6.0890000000000004</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="16" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A16" s="66" t="s">
         <v>78</v>
       </c>
@@ -31349,7 +31349,7 @@
         <v>14.34</v>
       </c>
     </row>
-    <row r="17" spans="1:10" s="8" customFormat="1" ht="11.25">
+    <row r="17" spans="1:10" s="8" customFormat="1" ht="11.4">
       <c r="A17" s="67" t="s">
         <v>39</v>
       </c>
@@ -31395,7 +31395,7 @@
       <c r="I18" s="32"/>
       <c r="J18" s="32"/>
     </row>
-    <row r="19" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="19" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A19" s="66" t="s">
         <v>17</v>
       </c>
@@ -31427,7 +31427,7 @@
         <v>-3.4</v>
       </c>
     </row>
-    <row r="20" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="20" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A20" s="66" t="s">
         <v>18</v>
       </c>
@@ -31459,7 +31459,7 @@
         <v>5.6609999999999996</v>
       </c>
     </row>
-    <row r="21" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="21" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A21" s="66" t="s">
         <v>19</v>
       </c>
@@ -31491,7 +31491,7 @@
         <v>8.9290000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="22" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A22" s="66" t="s">
         <v>78</v>
       </c>
@@ -31523,7 +31523,7 @@
         <v>9.2050000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:10" s="8" customFormat="1" ht="11.25">
+    <row r="23" spans="1:10" s="8" customFormat="1" ht="11.4">
       <c r="A23" s="67" t="s">
         <v>39</v>
       </c>
@@ -31569,7 +31569,7 @@
       <c r="I24" s="32"/>
       <c r="J24" s="32"/>
     </row>
-    <row r="25" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="25" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A25" s="66" t="s">
         <v>17</v>
       </c>
@@ -31601,7 +31601,7 @@
         <v>-4.0129999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="26" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A26" s="66" t="s">
         <v>18</v>
       </c>
@@ -31633,7 +31633,7 @@
         <v>-1.466</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="27" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A27" s="66" t="s">
         <v>19</v>
       </c>
@@ -31665,7 +31665,7 @@
         <v>0.27900000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="28" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A28" s="66" t="s">
         <v>78</v>
       </c>
@@ -31697,7 +31697,7 @@
         <v>52.185000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:10" s="8" customFormat="1" ht="11.25">
+    <row r="29" spans="1:10" s="8" customFormat="1" ht="11.4">
       <c r="A29" s="67" t="s">
         <v>39</v>
       </c>
@@ -31743,7 +31743,7 @@
       <c r="I30" s="32"/>
       <c r="J30" s="32"/>
     </row>
-    <row r="31" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="31" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A31" s="66" t="s">
         <v>17</v>
       </c>
@@ -31775,7 +31775,7 @@
         <v>-16.97</v>
       </c>
     </row>
-    <row r="32" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="32" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A32" s="66" t="s">
         <v>18</v>
       </c>
@@ -31807,7 +31807,7 @@
         <v>10.846</v>
       </c>
     </row>
-    <row r="33" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="33" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A33" s="66" t="s">
         <v>19</v>
       </c>
@@ -31839,7 +31839,7 @@
         <v>-1.5489999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="34" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A34" s="66" t="s">
         <v>78</v>
       </c>
@@ -31871,7 +31871,7 @@
         <v>13.398999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:10" s="8" customFormat="1" ht="11.25">
+    <row r="35" spans="1:10" s="8" customFormat="1" ht="11.4">
       <c r="A35" s="67" t="s">
         <v>39</v>
       </c>
@@ -31917,7 +31917,7 @@
       <c r="I36" s="32"/>
       <c r="J36" s="32"/>
     </row>
-    <row r="37" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="37" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A37" s="66" t="s">
         <v>17</v>
       </c>
@@ -31949,7 +31949,7 @@
         <v>-0.97</v>
       </c>
     </row>
-    <row r="38" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="38" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A38" s="66" t="s">
         <v>18</v>
       </c>
@@ -31981,7 +31981,7 @@
         <v>4.9450000000000003</v>
       </c>
     </row>
-    <row r="39" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="39" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A39" s="66" t="s">
         <v>19</v>
       </c>
@@ -32013,7 +32013,7 @@
         <v>-1.9410000000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="40" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A40" s="66" t="s">
         <v>78</v>
       </c>
@@ -32045,7 +32045,7 @@
         <v>-26.344999999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:10" s="8" customFormat="1" ht="11.25">
+    <row r="41" spans="1:10" s="8" customFormat="1" ht="11.4">
       <c r="A41" s="67" t="s">
         <v>39</v>
       </c>
@@ -32091,7 +32091,7 @@
       <c r="I42" s="32"/>
       <c r="J42" s="32"/>
     </row>
-    <row r="43" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="43" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A43" s="66" t="s">
         <v>17</v>
       </c>
@@ -32123,7 +32123,7 @@
         <v>-21.529</v>
       </c>
     </row>
-    <row r="44" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="44" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A44" s="66" t="s">
         <v>18</v>
       </c>
@@ -32155,7 +32155,7 @@
         <v>49.991999999999997</v>
       </c>
     </row>
-    <row r="45" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="45" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A45" s="66" t="s">
         <v>19</v>
       </c>
@@ -32187,7 +32187,7 @@
         <v>18.986000000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="46" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A46" s="66" t="s">
         <v>78</v>
       </c>
@@ -32219,7 +32219,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="47" spans="1:10" s="8" customFormat="1" ht="11.25">
+    <row r="47" spans="1:10" s="8" customFormat="1" ht="11.4">
       <c r="A47" s="67" t="s">
         <v>39</v>
       </c>
@@ -32265,7 +32265,7 @@
       <c r="I48" s="32"/>
       <c r="J48" s="32"/>
     </row>
-    <row r="49" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="49" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A49" s="66" t="s">
         <v>17</v>
       </c>
@@ -32297,7 +32297,7 @@
         <v>29.891999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="50" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A50" s="66" t="s">
         <v>18</v>
       </c>
@@ -32329,7 +32329,7 @@
         <v>-13.326000000000001</v>
       </c>
     </row>
-    <row r="51" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="51" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A51" s="66" t="s">
         <v>19</v>
       </c>
@@ -32361,7 +32361,7 @@
         <v>0.94399999999999995</v>
       </c>
     </row>
-    <row r="52" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="52" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A52" s="66" t="s">
         <v>78</v>
       </c>
@@ -32393,7 +32393,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="53" spans="1:10" s="8" customFormat="1" ht="11.25">
+    <row r="53" spans="1:10" s="8" customFormat="1" ht="11.4">
       <c r="A53" s="67" t="s">
         <v>39</v>
       </c>
@@ -32439,7 +32439,7 @@
       <c r="I54" s="32"/>
       <c r="J54" s="32"/>
     </row>
-    <row r="55" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="55" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A55" s="66" t="s">
         <v>17</v>
       </c>
@@ -32471,7 +32471,7 @@
         <v>-1.458</v>
       </c>
     </row>
-    <row r="56" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="56" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A56" s="66" t="s">
         <v>18</v>
       </c>
@@ -32503,7 +32503,7 @@
         <v>-0.85499999999999998</v>
       </c>
     </row>
-    <row r="57" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="57" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A57" s="66" t="s">
         <v>19</v>
       </c>
@@ -32535,7 +32535,7 @@
         <v>1.046</v>
       </c>
     </row>
-    <row r="58" spans="1:10" s="34" customFormat="1" ht="11.25">
+    <row r="58" spans="1:10" s="34" customFormat="1" ht="11.4">
       <c r="A58" s="66" t="s">
         <v>78</v>
       </c>
@@ -32567,7 +32567,7 @@
         <v>10.923999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:10" s="8" customFormat="1" ht="11.25">
+    <row r="59" spans="1:10" s="8" customFormat="1" ht="11.4">
       <c r="A59" s="67" t="s">
         <v>39</v>
       </c>
@@ -32739,17 +32739,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K68"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" style="36" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" style="37" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="8.28515625" style="37" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" style="36" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" style="37" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="8.33203125" style="37" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="7" style="37" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" style="37" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.28515625" style="36"/>
+    <col min="10" max="10" width="9.5546875" style="37" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.33203125" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15">
+    <row r="1" spans="1:11" ht="14.4">
       <c r="A1" s="63"/>
       <c r="K1"/>
     </row>
@@ -32771,7 +32771,7 @@
       <c r="J3" s="65"/>
       <c r="K3"/>
     </row>
-    <row r="4" spans="1:11" s="16" customFormat="1" ht="14.25">
+    <row r="4" spans="1:11" s="16" customFormat="1" ht="15">
       <c r="A4" s="32"/>
       <c r="B4" s="12" t="s">
         <v>0</v>
@@ -33085,7 +33085,7 @@
         <v>3298.1129999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="14.25">
+    <row r="15" spans="1:11" ht="13.8">
       <c r="A15" s="79" t="s">
         <v>238</v>
       </c>
@@ -33457,7 +33457,7 @@
       <c r="I28" s="32"/>
       <c r="J28" s="32"/>
     </row>
-    <row r="29" spans="1:10" ht="14.25">
+    <row r="29" spans="1:10" ht="15">
       <c r="A29" s="95" t="s">
         <v>325</v>
       </c>
@@ -33727,7 +33727,7 @@
         <v>3097.8719999999998</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="14.25">
+    <row r="38" spans="1:10" ht="13.8">
       <c r="A38" s="79" t="s">
         <v>238</v>
       </c>
